--- a/uploads/Phones.xlsx
+++ b/uploads/Phones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Git Project\Warehouse\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20764CD-C04F-4F6B-A6DE-E283F6E882C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BB196B-2A68-45E9-BEB9-23E9B4192ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31500" yWindow="2700" windowWidth="15300" windowHeight="7725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
